--- a/santhosh/Assets/3A_Catalog/Workflow_Centra.xlsx
+++ b/santhosh/Assets/3A_Catalog/Workflow_Centra.xlsx
@@ -4267,7 +4267,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F47"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22.84"/>
@@ -5795,7 +5795,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="639.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="708.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
         <v>228</v>
       </c>
@@ -5821,7 +5821,7 @@
       <c r="K2" s="15"/>
       <c r="L2" s="15"/>
     </row>
-    <row r="3" customFormat="false" ht="293.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="298.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9"/>
       <c r="B3" s="9" t="s">
         <v>234</v>
@@ -5847,7 +5847,7 @@
       <c r="K3" s="15"/>
       <c r="L3" s="15"/>
     </row>
-    <row r="4" customFormat="false" ht="427.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="426.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9"/>
       <c r="B4" s="9" t="s">
         <v>239</v>
@@ -5920,9 +5920,6 @@
       <c r="L6" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:A5"/>
-  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -6533,7 +6530,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C38"/>
-  <sheetFormatPr defaultColWidth="12.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.07421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="39" width="46.44"/>
